--- a/data/trans_orig/P05A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>680722</t>
+          <t>682884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>737024</t>
+          <t>739182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>926533</t>
+          <t>927300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>994194</t>
+          <t>990908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1632501</t>
+          <t>1625834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1715837</t>
+          <t>1718074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197252</t>
+          <t>198838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250559</t>
+          <t>252909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>297464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362050</t>
+          <t>363079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510480</t>
+          <t>510132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592709</t>
+          <t>596819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56069</t>
+          <t>55257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>57419</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90797</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1326798</t>
+          <t>1327042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1405724</t>
+          <t>1413425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1177878</t>
+          <t>1180796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1260828</t>
+          <t>1257878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2526336</t>
+          <t>2535677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2644609</t>
+          <t>2646863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>464049</t>
+          <t>460349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>541774</t>
+          <t>541035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422254</t>
+          <t>422966</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>498078</t>
+          <t>497390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>903144</t>
+          <t>905359</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1017290</t>
+          <t>1012052</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66838</t>
+          <t>66952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104957</t>
+          <t>104042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52208</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86990</t>
+          <t>84879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126843</t>
+          <t>125676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177148</t>
+          <t>176678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316528</t>
+          <t>317521</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>361764</t>
+          <t>360838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310542</t>
+          <t>311141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351021</t>
+          <t>349799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>641894</t>
+          <t>641492</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701795</t>
+          <t>701903</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101333</t>
+          <t>100087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142688</t>
+          <t>140010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96693</t>
+          <t>98525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136812</t>
+          <t>136542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>208726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265816</t>
+          <t>265972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41682</t>
+          <t>40886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2359038</t>
+          <t>2361193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2474675</t>
+          <t>2474452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2452485</t>
+          <t>2456641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2562196</t>
+          <t>2566954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4846829</t>
+          <t>4849649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5010063</t>
+          <t>5005286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>794188</t>
+          <t>794774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>901126</t>
+          <t>898585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>852431</t>
+          <t>851726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>961071</t>
+          <t>958579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1670573</t>
+          <t>1674775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1824406</t>
+          <t>1827716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112310</t>
+          <t>111143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162203</t>
+          <t>160505</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99414</t>
+          <t>97761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144751</t>
+          <t>140484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224186</t>
+          <t>222488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>286182</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>537958</t>
+          <t>534081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>582693</t>
+          <t>579652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>692206</t>
+          <t>694378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>751349</t>
+          <t>752164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1247583</t>
+          <t>1242439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1321730</t>
+          <t>1319016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138149</t>
+          <t>138335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180776</t>
+          <t>182338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>194324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250094</t>
+          <t>248235</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342393</t>
+          <t>346199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>413486</t>
+          <t>418400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>22146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54687</t>
+          <t>55790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88759</t>
+          <t>91368</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1543554</t>
+          <t>1542918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1622341</t>
+          <t>1620356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1475372</t>
+          <t>1471104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1549216</t>
+          <t>1548432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3036918</t>
+          <t>3036169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3144501</t>
+          <t>3146626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>369725</t>
+          <t>372389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>445424</t>
+          <t>446331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>363266</t>
+          <t>363931</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>433937</t>
+          <t>437454</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>759682</t>
+          <t>754333</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>860386</t>
+          <t>863135</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>59329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95330</t>
+          <t>91564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83919</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119070</t>
+          <t>118666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165253</t>
+          <t>164881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>398322</t>
+          <t>399358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>440311</t>
+          <t>440738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>408175</t>
+          <t>408420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>446033</t>
+          <t>446336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>819667</t>
+          <t>820678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>875175</t>
+          <t>875889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95553</t>
+          <t>93711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135019</t>
+          <t>133651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83629</t>
+          <t>81970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119407</t>
+          <t>118691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187382</t>
+          <t>187931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240770</t>
+          <t>241372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2515673</t>
+          <t>2510614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2612688</t>
+          <t>2613115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2608756</t>
+          <t>2612365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2712306</t>
+          <t>2716856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5148836</t>
+          <t>5151320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5293647</t>
+          <t>5293638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>631403</t>
+          <t>631241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>727045</t>
+          <t>727216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>671418</t>
+          <t>671601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>770091</t>
+          <t>767321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332338</t>
+          <t>1334216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1469039</t>
+          <t>1468802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98547</t>
+          <t>97538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141472</t>
+          <t>141922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96843</t>
+          <t>99758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144333</t>
+          <t>144679</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>210206</t>
+          <t>206688</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>271021</t>
+          <t>268813</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>394705</t>
+          <t>394500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>426555</t>
+          <t>427756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>584017</t>
+          <t>583562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>619259</t>
+          <t>619851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>987988</t>
+          <t>986761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1035348</t>
+          <t>1035587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50487</t>
+          <t>51096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>77966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93161</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122873</t>
+          <t>124206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152572</t>
+          <t>151119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194330</t>
+          <t>194163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27642</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49521</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>67701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97636</t>
+          <t>98612</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1902588</t>
+          <t>1901634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2061435</t>
+          <t>2045504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1830700</t>
+          <t>1827783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1982882</t>
+          <t>1978211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3754877</t>
+          <t>3753318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3978314</t>
+          <t>3989189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166747</t>
+          <t>174626</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279245</t>
+          <t>283434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>192190</t>
+          <t>194098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>308206</t>
+          <t>310492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>406637</t>
+          <t>399624</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>573204</t>
+          <t>572911</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60427</t>
+          <t>58636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119407</t>
+          <t>115994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60816</t>
+          <t>60734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107240</t>
+          <t>108094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137956</t>
+          <t>138359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213346</t>
+          <t>216244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -5749,17 +5749,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>532256</t>
+          <t>532257</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>505082</t>
+          <t>503749</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>554654</t>
+          <t>555784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533644</t>
+          <t>530649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>568059</t>
+          <t>567356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1051027</t>
+          <t>1051021</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1113216</t>
+          <t>1110012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73309</t>
+          <t>73454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121263</t>
+          <t>123825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73139</t>
+          <t>73299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106615</t>
+          <t>109476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157945</t>
+          <t>159800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216534</t>
+          <t>218674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>32803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25657</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49296</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -6088,17 +6088,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645520</t>
+          <t>645521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645520</t>
+          <t>645521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645520</t>
+          <t>645521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2841114</t>
+          <t>2830394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3019090</t>
+          <t>3017602</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2977713</t>
+          <t>2978150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3146111</t>
+          <t>3147234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5836914</t>
+          <t>5838884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6078846</t>
+          <t>6083871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309564</t>
+          <t>305598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>446989</t>
+          <t>447969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376942</t>
+          <t>372786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>511332</t>
+          <t>508794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743902</t>
+          <t>741842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>940960</t>
+          <t>934382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107726</t>
+          <t>109973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178188</t>
+          <t>176978</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117589</t>
+          <t>119432</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171402</t>
+          <t>171537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>247913</t>
+          <t>244476</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>332919</t>
+          <t>332634</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>682884</t>
+          <t>685422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>739182</t>
+          <t>738012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>927300</t>
+          <t>924363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>990908</t>
+          <t>993019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1625834</t>
+          <t>1625254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1718074</t>
+          <t>1712600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198838</t>
+          <t>198056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252909</t>
+          <t>248875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297464</t>
+          <t>297824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>363079</t>
+          <t>363820</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510132</t>
+          <t>513591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596819</t>
+          <t>599209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44150</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55257</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57419</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90274</t>
+          <t>89918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1327042</t>
+          <t>1328714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1413425</t>
+          <t>1412758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1180796</t>
+          <t>1173997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1257878</t>
+          <t>1256286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2535677</t>
+          <t>2527008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2646863</t>
+          <t>2640957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>460349</t>
+          <t>461237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>541035</t>
+          <t>540300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422966</t>
+          <t>424880</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>497390</t>
+          <t>500972</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>905359</t>
+          <t>910500</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1012052</t>
+          <t>1016445</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66952</t>
+          <t>66556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104042</t>
+          <t>105463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>51230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84879</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125676</t>
+          <t>127304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176678</t>
+          <t>173817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>317521</t>
+          <t>318284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>360838</t>
+          <t>359382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>310484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349799</t>
+          <t>350745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>641492</t>
+          <t>641872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701903</t>
+          <t>700512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100087</t>
+          <t>103017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140010</t>
+          <t>141591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98525</t>
+          <t>98065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136542</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>208726</t>
+          <t>209566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265972</t>
+          <t>266566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2361193</t>
+          <t>2365145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2474452</t>
+          <t>2480110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2456641</t>
+          <t>2453729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2566954</t>
+          <t>2568022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4849649</t>
+          <t>4847495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5005286</t>
+          <t>5011483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>794774</t>
+          <t>787888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>898585</t>
+          <t>899222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>851726</t>
+          <t>853540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>958579</t>
+          <t>959653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1674775</t>
+          <t>1676989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1827716</t>
+          <t>1835151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111143</t>
+          <t>111099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160505</t>
+          <t>160694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97761</t>
+          <t>98121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>140484</t>
+          <t>141977</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>222488</t>
+          <t>220403</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>290746</t>
+          <t>288214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>534081</t>
+          <t>532453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>579652</t>
+          <t>580389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>694378</t>
+          <t>695029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>752164</t>
+          <t>751644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1242439</t>
+          <t>1248469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1319016</t>
+          <t>1324268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138335</t>
+          <t>139816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182338</t>
+          <t>183583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194324</t>
+          <t>194023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248235</t>
+          <t>249249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346199</t>
+          <t>343734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>418400</t>
+          <t>413692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22146</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44324</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55790</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91368</t>
+          <t>89132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1542918</t>
+          <t>1545681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1620356</t>
+          <t>1619632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1471104</t>
+          <t>1473597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1548432</t>
+          <t>1548200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3036169</t>
+          <t>3035257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3146626</t>
+          <t>3150387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>372389</t>
+          <t>374546</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>446331</t>
+          <t>448431</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>363931</t>
+          <t>362331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>437454</t>
+          <t>435744</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>754333</t>
+          <t>750128</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>863135</t>
+          <t>860972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59329</t>
+          <t>58380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91564</t>
+          <t>94750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81243</t>
+          <t>83389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118666</t>
+          <t>115198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164881</t>
+          <t>162704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>399358</t>
+          <t>396955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>440738</t>
+          <t>438394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>408420</t>
+          <t>406585</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>446336</t>
+          <t>447722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>820678</t>
+          <t>818204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>875889</t>
+          <t>874884</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>94773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133651</t>
+          <t>136168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81970</t>
+          <t>81696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118691</t>
+          <t>119451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187931</t>
+          <t>188089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241372</t>
+          <t>243273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21125</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>38997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2510614</t>
+          <t>2511123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2613115</t>
+          <t>2611026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2612365</t>
+          <t>2611936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2716856</t>
+          <t>2717348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5151320</t>
+          <t>5158763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5293638</t>
+          <t>5294430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>631241</t>
+          <t>636204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>727216</t>
+          <t>726391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>671601</t>
+          <t>667634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>767321</t>
+          <t>768175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1334216</t>
+          <t>1330117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1468802</t>
+          <t>1462834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97538</t>
+          <t>97363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141922</t>
+          <t>140689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99758</t>
+          <t>97093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144679</t>
+          <t>141631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>206688</t>
+          <t>206050</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>268813</t>
+          <t>268498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>410881</t>
+          <t>460438</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>394500</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>427756</t>
+          <t>478105</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4872,32 +4872,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>601527</t>
+          <t>650639</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>583562</t>
+          <t>632778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>619851</t>
+          <t>667638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1012409</t>
+          <t>1111077</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>986761</t>
+          <t>1085242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1035587</t>
+          <t>1137888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63225</t>
+          <t>72980</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4985,32 +4985,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>107704</t>
+          <t>119108</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92627</t>
+          <t>103904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124206</t>
+          <t>136173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,32 +5020,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>170929</t>
+          <t>192087</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151119</t>
+          <t>169502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194163</t>
+          <t>214769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -5063,32 +5063,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>41561</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5098,32 +5098,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>49853</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>40025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>62584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>81707</t>
+          <t>91414</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67701</t>
+          <t>75779</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98612</t>
+          <t>108167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>511808</t>
+          <t>574978</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511808</t>
+          <t>574978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>511808</t>
+          <t>574978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>753236</t>
+          <t>819600</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>753236</t>
+          <t>819600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>753236</t>
+          <t>819600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1265045</t>
+          <t>1394578</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1265045</t>
+          <t>1394578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1265045</t>
+          <t>1394578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5293,32 +5293,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1959223</t>
+          <t>1866081</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1901634</t>
+          <t>1821563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2045504</t>
+          <t>1904838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1885420</t>
+          <t>1768975</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1827783</t>
+          <t>1732206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1978211</t>
+          <t>1803542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3844642</t>
+          <t>3635056</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3753318</t>
+          <t>3583526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3989189</t>
+          <t>3689612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>236062</t>
+          <t>262020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174626</t>
+          <t>226431</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>283434</t>
+          <t>298070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>263527</t>
+          <t>295268</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194098</t>
+          <t>266523</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>310492</t>
+          <t>325946</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>499589</t>
+          <t>557288</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>399624</t>
+          <t>510560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>572911</t>
+          <t>602779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -5519,32 +5519,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89229</t>
+          <t>96795</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58636</t>
+          <t>76589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115994</t>
+          <t>124633</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5554,32 +5554,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>102573</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60734</t>
+          <t>82982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108094</t>
+          <t>124464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>174320</t>
+          <t>199368</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138359</t>
+          <t>168056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216244</t>
+          <t>232234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5632,17 +5632,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2284514</t>
+          <t>2224896</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2284514</t>
+          <t>2224896</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2284514</t>
+          <t>2224896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5667,17 +5667,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2234037</t>
+          <t>2166816</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2234037</t>
+          <t>2166816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2234037</t>
+          <t>2166816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4518551</t>
+          <t>4391712</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4518551</t>
+          <t>4391712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4518551</t>
+          <t>4391712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>532257</t>
+          <t>592012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>503749</t>
+          <t>563435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>555784</t>
+          <t>611726</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>551810</t>
+          <t>610202</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>530649</t>
+          <t>587349</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>567356</t>
+          <t>627079</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1084067</t>
+          <t>1202214</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1051021</t>
+          <t>1173158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1110012</t>
+          <t>1229660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -5862,32 +5862,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95180</t>
+          <t>98207</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73454</t>
+          <t>81361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123825</t>
+          <t>125642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5897,32 +5897,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88861</t>
+          <t>100972</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73299</t>
+          <t>84812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109476</t>
+          <t>121295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>184041</t>
+          <t>199179</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159800</t>
+          <t>173876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218674</t>
+          <t>226240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -5975,22 +5975,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6010,67 +6010,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>38847</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>27443</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>54411</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>3,78%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>34296</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>23808</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>49000</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -6088,17 +6088,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645521</t>
+          <t>710296</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645521</t>
+          <t>710296</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645521</t>
+          <t>710296</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6123,17 +6123,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>656884</t>
+          <t>729944</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>656884</t>
+          <t>729944</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>656884</t>
+          <t>729944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1302404</t>
+          <t>1440240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1302404</t>
+          <t>1440240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1302404</t>
+          <t>1440240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2902361</t>
+          <t>2918531</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2830394</t>
+          <t>2866687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3017602</t>
+          <t>2970466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6240,32 +6240,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3038757</t>
+          <t>3029815</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2978150</t>
+          <t>2983139</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3147234</t>
+          <t>3072552</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5941118</t>
+          <t>5948347</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5838884</t>
+          <t>5885907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6083871</t>
+          <t>6021278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -6318,32 +6318,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>394467</t>
+          <t>433206</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>305598</t>
+          <t>389440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447969</t>
+          <t>477223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6353,32 +6353,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>460092</t>
+          <t>515348</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>372786</t>
+          <t>479180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>508794</t>
+          <t>556855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,32 +6388,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>854559</t>
+          <t>948554</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>741842</t>
+          <t>891070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>934382</t>
+          <t>1008195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6431,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145015</t>
+          <t>158433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109973</t>
+          <t>133164</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176978</t>
+          <t>189178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145308</t>
+          <t>171197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119432</t>
+          <t>146327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171537</t>
+          <t>195960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>290323</t>
+          <t>329630</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244476</t>
+          <t>293524</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>332634</t>
+          <t>368272</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -6544,17 +6544,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3441843</t>
+          <t>3510170</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3441843</t>
+          <t>3510170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3441843</t>
+          <t>3510170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3644157</t>
+          <t>3716360</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3644157</t>
+          <t>3716360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3644157</t>
+          <t>3716360</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7086000</t>
+          <t>7226530</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7086000</t>
+          <t>7226530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7086000</t>
+          <t>7226530</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
